--- a/data/1.abstracting/26_02_01_deduplicated_processed.xlsx
+++ b/data/1.abstracting/26_02_01_deduplicated_processed.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unipdit-my.sharepoint.com/personal/tommaso_feraco_unipd_it/Documents/BESSI/living_SEB_review/data/1.abstracting/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5DDEBE19-AF01-48E7-A2F5-3C402F1862AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="8_{5DDEBE19-AF01-48E7-A2F5-3C402F1862AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F7ABE66A-7CE4-4348-93A6-3613764A9E32}"/>
   <bookViews>
-    <workbookView xWindow="43095" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{E8FC1A4C-D294-41E5-B5E0-E778460E2170}"/>
+    <workbookView xWindow="47235" yWindow="765" windowWidth="9600" windowHeight="9720" xr2:uid="{E8FC1A4C-D294-41E5-B5E0-E778460E2170}"/>
   </bookViews>
   <sheets>
     <sheet name="26_02_01_deduplicated_processed" sheetId="1" r:id="rId1"/>
@@ -61,9 +61,6 @@
     <t>Using an exploratory quasi-experimental design, the present research investigated SEB skills as an antecedent and consequence of volunteering in a sample of college students who were either actively volunteering (N = 169) or not (N = 286). Results indicated that more skilled students participated in volunteering, but volunteering, in general, did not predict positive SEB skill change. However, participants who reported interacting with others while volunteering experienced growth in socially relevant skills. Participants who reported positive subjective evaluations of volunteering also experienced growth in several SEB skills. These findings suggest that domain relevant actions, as well as subjective experiences of engaging in those actions, may be critical for positive SEB skill development. Â© 2026 Elsevier Inc.</t>
   </si>
   <si>
-    <t>10.1016/j.jrp.2026.104705</t>
-  </si>
-  <si>
     <t>rayyan-450915335</t>
   </si>
   <si>
@@ -109,9 +106,6 @@
     <t>Finding a job that fits is widely recognized as important for personal fulfillment and professional success. Despite the long history of person-environment fit research, surprisingly little is known about person-job fit in terms of basic personality traits. This study examined three basic tenets of fit theory regarding personality-job fit: Fit (1) is pleasurable, (2) regulated by individuals, and (3) changes over time. We hypothesized that personality-job fit would be associated with higher subjective well-being (RQ1), predict less occupational change (RQ2), and vary across the professional lifespan (RQ3). Fit was conceptualized as ``broad congruence{''} between individuals' Big Five trait levels and expert-rated trait demands of their occupations. We used nationally representative data from German jobholders (N = 18,712-30,883). Multilevel polynomial regression and response surface analysis showed no significant congruence effects but some interactions: More extraverted and open individuals felt better and were less likely to leave their jobs when these traits were strongly demanded by their work, though these outcomes were not optimized at exact personality-job fit. Additionally, personality-job fit improved over time, showing a linear increase across the lifespan. These findings emphasize studying fit theories in detail and considering individuals' personalities, such as being communicative or original, in career choice.</t>
   </si>
   <si>
-    <t>10.1177/08902070251409430</t>
-  </si>
-  <si>
     <t>rayyan-450915339</t>
   </si>
   <si>
@@ -127,9 +121,6 @@
     <t>The research aims to analyze changes in agreeableness and its subcomponents: empathy, respect, and trust during and after the COVID-19 pandemic (2021-2024), while evaluating demographic influences of education level and gender. This trend study used independent samples of adolescents, collected annually from 2021 to 2024. The data collection instrument was the Agreeableness Scale from the Semente Panel of Socioemotional Skills. We conducted comparative analyses to identify significant differences in the scores of overall agreeableness and its subcomponents, based on the year of data collection, educational level (upper elementary school vs. high school), and gender. We observed a significant drop in agreeableness scores in 2022 and 2023, a period marked by the prolonged impacts of the COVID-19 pandemic. In 2024, we identified a recovery in the levels of this skill. Students in upper elementary school had higher agreeableness scores compared to those in high school. Regarding gender, female high school students showed higher levels of empathy and respect, while upper elementary school students showed greater trust.The socioemotional skills analyzed were affected by the COVID-19 pandemic and showed changes over time, according to the education level and gender. The results support the importance of promoting educational interventions aimed at strengthening socioemotional development, especially in times of crisis, to foster students' social adaptation.</t>
   </si>
   <si>
-    <t>10.1007/s12187-025-10326-7</t>
-  </si>
-  <si>
     <t>decision</t>
   </si>
   <si>
@@ -137,13 +128,22 @@
   </si>
   <si>
     <t>exclude</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1016/j.jrp.2026.104705</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1177/08902070251409430</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1007/s12187-025-10326-7</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -274,6 +274,14 @@
     <font>
       <sz val="11"/>
       <color theme="0"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -576,7 +584,7 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="42">
+  <cellStyleXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
@@ -619,11 +627,13 @@
     <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="42"/>
   </cellXfs>
-  <cellStyles count="42">
+  <cellStyles count="43">
     <cellStyle name="20% - Colore 1" xfId="19" builtinId="30" customBuiltin="1"/>
     <cellStyle name="20% - Colore 2" xfId="23" builtinId="34" customBuiltin="1"/>
     <cellStyle name="20% - Colore 3" xfId="27" builtinId="38" customBuiltin="1"/>
@@ -645,6 +655,7 @@
     <cellStyle name="Calcolo" xfId="11" builtinId="22" customBuiltin="1"/>
     <cellStyle name="Cella collegata" xfId="12" builtinId="24" customBuiltin="1"/>
     <cellStyle name="Cella da controllare" xfId="13" builtinId="23" customBuiltin="1"/>
+    <cellStyle name="Collegamento ipertestuale" xfId="42" builtinId="8"/>
     <cellStyle name="Colore 1" xfId="18" builtinId="29" customBuiltin="1"/>
     <cellStyle name="Colore 2" xfId="22" builtinId="33" customBuiltin="1"/>
     <cellStyle name="Colore 3" xfId="26" builtinId="37" customBuiltin="1"/>
@@ -1026,15 +1037,15 @@
         <v>6</v>
       </c>
       <c r="I1" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>8</v>
       </c>
-      <c r="C2" t="s">
-        <v>13</v>
+      <c r="C2" s="1" t="s">
+        <v>36</v>
       </c>
       <c r="D2">
         <v>2026</v>
@@ -1052,108 +1063,113 @@
         <v>12</v>
       </c>
       <c r="I2" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D3">
         <v>2025</v>
       </c>
       <c r="E3" t="s">
+        <v>15</v>
+      </c>
+      <c r="F3" t="s">
         <v>16</v>
       </c>
-      <c r="F3" t="s">
+      <c r="G3" t="s">
+        <v>14</v>
+      </c>
+      <c r="H3" t="s">
         <v>17</v>
       </c>
-      <c r="G3" t="s">
-        <v>15</v>
-      </c>
-      <c r="H3" t="s">
-        <v>18</v>
-      </c>
       <c r="I3" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D4">
         <v>2025</v>
       </c>
       <c r="E4" t="s">
+        <v>20</v>
+      </c>
+      <c r="F4" t="s">
         <v>21</v>
       </c>
-      <c r="F4" t="s">
+      <c r="G4" t="s">
+        <v>19</v>
+      </c>
+      <c r="H4" t="s">
         <v>22</v>
       </c>
-      <c r="G4" t="s">
-        <v>20</v>
-      </c>
-      <c r="H4" t="s">
-        <v>23</v>
-      </c>
       <c r="I4" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C5" t="s">
-        <v>29</v>
+        <v>23</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="D5">
         <v>2026</v>
       </c>
       <c r="E5" t="s">
+        <v>25</v>
+      </c>
+      <c r="F5" t="s">
         <v>26</v>
       </c>
-      <c r="F5" t="s">
+      <c r="G5" t="s">
+        <v>24</v>
+      </c>
+      <c r="H5" t="s">
         <v>27</v>
       </c>
-      <c r="G5" t="s">
-        <v>25</v>
-      </c>
-      <c r="H5" t="s">
-        <v>28</v>
-      </c>
       <c r="I5" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>30</v>
-      </c>
-      <c r="C6" t="s">
-        <v>35</v>
+        <v>28</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>38</v>
       </c>
       <c r="D6">
         <v>2026</v>
       </c>
       <c r="E6" t="s">
+        <v>30</v>
+      </c>
+      <c r="F6" t="s">
+        <v>31</v>
+      </c>
+      <c r="G6" t="s">
+        <v>29</v>
+      </c>
+      <c r="H6" t="s">
         <v>32</v>
       </c>
-      <c r="F6" t="s">
-        <v>33</v>
-      </c>
-      <c r="G6" t="s">
-        <v>31</v>
-      </c>
-      <c r="H6" t="s">
+      <c r="I6" t="s">
         <v>34</v>
-      </c>
-      <c r="I6" t="s">
-        <v>37</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="C2" r:id="rId1" xr:uid="{B175AC9B-2C61-4F94-BE30-FBBC65988A50}"/>
+    <hyperlink ref="C5" r:id="rId2" xr:uid="{3A6E828C-1614-4FB4-8394-4C4FEFF5D9C8}"/>
+    <hyperlink ref="C6" r:id="rId3" xr:uid="{6F5A5984-AF12-4830-81C3-3FCAC7AD4FE5}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>